--- a/request_forms/008_student_staff_reference_request_form--request_forms.xlsx
+++ b/request_forms/008_student_staff_reference_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'referee_1',_'value':_'referee1'}</t>
+          <t>referee_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 1', 'value': 'referee1'}</t>
+          <t>Referee 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'referee_2',_'value':_'referee2'}</t>
+          <t>referee_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 2', 'value': 'referee2'}</t>
+          <t>Referee 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'referee_3',_'value':_'referee3'}</t>
+          <t>referee_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 3', 'value': 'referee3'}</t>
+          <t>Referee 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'referee_4',_'value':_'referee4'}</t>
+          <t>referee_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 4', 'value': 'referee4'}</t>
+          <t>Referee 4</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'referee_5',_'value':_'referee5'}</t>
+          <t>referee_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 5', 'value': 'referee5'}</t>
+          <t>Referee 5</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'referee_6',_'value':_'referee6'}</t>
+          <t>referee_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 6', 'value': 'referee6'}</t>
+          <t>Referee 6</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'referee_7',_'value':_'referee7'}</t>
+          <t>referee_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 7', 'value': 'referee7'}</t>
+          <t>Referee 7</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'referee_8',_'value':_'referee8'}</t>
+          <t>referee_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 8', 'value': 'referee8'}</t>
+          <t>Referee 8</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'referee_9',_'value':_'referee9'}</t>
+          <t>referee_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 9', 'value': 'referee9'}</t>
+          <t>Referee 9</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'referee_10',_'value':_'referee10'}</t>
+          <t>referee_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Referee 10', 'value': 'referee10'}</t>
+          <t>Referee 10</t>
         </is>
       </c>
     </row>
